--- a/SBM-corps-FHIR/ig/StructureDefinition-fr-vaccin-recommande-document.xlsx
+++ b/SBM-corps-FHIR/ig/StructureDefinition-fr-vaccin-recommande-document.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$74</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$73</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2680" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2645" uniqueCount="432">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-09-03T12:41:15+00:00</t>
+    <t>2025-09-04T10:23:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,10 +84,10 @@
     <t>Description</t>
   </si>
   <si>
-    <t>L'entrée 'Vaccin recommandé' est une entrée de type 'substanceAdministration' qui permet de décrire une vaccination prévue ou proposée.
+    <t>FrVaccinRecommandeDocument permet de décrire une vaccination prévue ou proposée.
  - Une vaccination proposée est une proposition qui est utilisée dans la prise de décisions (elle peut apparaître comme une contribution ou un résultat provenant de l'aide à la décision clinique). 
  - Une vaccination prévue dépend d'un plan accepté et à venir.
- - Cette entrée hérite de la structuration, des contraintes et des vocabulaires de l'entrée 'Immunization' (1.3.6.1.4.1.19376.1.5.3.1.4.12)..</t>
+ - Ce profil hérite de la structuration, des contraintes et des vocabulaires définis dans le profil FrVaccinationDocument.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -465,7 +465,7 @@
 </t>
   </si>
   <si>
-    <t>Fr Vaccination Type</t>
+    <t>Extension - Fr Vaccination Type</t>
   </si>
   <si>
     <t>Extension représentant le type de vaccination (ex: INITIMMUNIZ, BOOSTER, IMMUNIZ), équivalent au code de l'entrée CDA FR-Vaccination.</t>
@@ -793,10 +793,10 @@
 </t>
   </si>
   <si>
-    <t>Fr Prescription</t>
-  </si>
-  <si>
-    <t>Instructions de prescription associées à l'administration du produit de santé.</t>
+    <t>Extension - Fr Prescription</t>
+  </si>
+  <si>
+    <t>Extension permettant d’indiquer les instructions de prescription associées à l'administration du produit de santé.</t>
   </si>
   <si>
     <t>ImmunizationRecommendation.modifierExtension</t>
@@ -1021,50 +1021,37 @@
     <t>ImmunizationRecommendation.recommendation.vaccineCode.extension.value[x]</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
-  </si>
-  <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.extension:translation.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.extension:translation.value[x]:valueCodeableConcept.id</t>
+    <t>ImmunizationRecommendation.recommendation.vaccineCode.extension:translation.value[x].id</t>
   </si>
   <si>
     <t>ImmunizationRecommendation.recommendation.vaccineCode.extension.value[x].id</t>
   </si>
   <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.extension:translation.value[x]:valueCodeableConcept.extension</t>
+    <t>ImmunizationRecommendation.recommendation.vaccineCode.extension:translation.value[x].extension</t>
   </si>
   <si>
     <t>ImmunizationRecommendation.recommendation.vaccineCode.extension.value[x].extension</t>
   </si>
   <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.extension:translation.value[x]:valueCodeableConcept.coding</t>
+    <t>ImmunizationRecommendation.recommendation.vaccineCode.extension:translation.value[x].coding</t>
   </si>
   <si>
     <t>ImmunizationRecommendation.recommendation.vaccineCode.extension.value[x].coding</t>
   </si>
   <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.extension:translation.value[x]:valueCodeableConcept.coding.id</t>
+    <t>ImmunizationRecommendation.recommendation.vaccineCode.extension:translation.value[x].coding.id</t>
   </si>
   <si>
     <t>ImmunizationRecommendation.recommendation.vaccineCode.extension.value[x].coding.id</t>
   </si>
   <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.extension:translation.value[x]:valueCodeableConcept.coding.extension</t>
+    <t>ImmunizationRecommendation.recommendation.vaccineCode.extension:translation.value[x].coding.extension</t>
   </si>
   <si>
     <t>ImmunizationRecommendation.recommendation.vaccineCode.extension.value[x].coding.extension</t>
   </si>
   <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.extension:translation.value[x]:valueCodeableConcept.coding.system</t>
+    <t>ImmunizationRecommendation.recommendation.vaccineCode.extension:translation.value[x].coding.system</t>
   </si>
   <si>
     <t>ImmunizationRecommendation.recommendation.vaccineCode.extension.value[x].coding.system</t>
@@ -1073,31 +1060,31 @@
     <t>https://interop.esante.gouv.fr/ig/document/core/ValueSet/fr-doc-vs-vaccine-translation</t>
   </si>
   <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.extension:translation.value[x]:valueCodeableConcept.coding.version</t>
+    <t>ImmunizationRecommendation.recommendation.vaccineCode.extension:translation.value[x].coding.version</t>
   </si>
   <si>
     <t>ImmunizationRecommendation.recommendation.vaccineCode.extension.value[x].coding.version</t>
   </si>
   <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.extension:translation.value[x]:valueCodeableConcept.coding.code</t>
+    <t>ImmunizationRecommendation.recommendation.vaccineCode.extension:translation.value[x].coding.code</t>
   </si>
   <si>
     <t>ImmunizationRecommendation.recommendation.vaccineCode.extension.value[x].coding.code</t>
   </si>
   <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.extension:translation.value[x]:valueCodeableConcept.coding.display</t>
+    <t>ImmunizationRecommendation.recommendation.vaccineCode.extension:translation.value[x].coding.display</t>
   </si>
   <si>
     <t>ImmunizationRecommendation.recommendation.vaccineCode.extension.value[x].coding.display</t>
   </si>
   <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.extension:translation.value[x]:valueCodeableConcept.coding.userSelected</t>
+    <t>ImmunizationRecommendation.recommendation.vaccineCode.extension:translation.value[x].coding.userSelected</t>
   </si>
   <si>
     <t>ImmunizationRecommendation.recommendation.vaccineCode.extension.value[x].coding.userSelected</t>
   </si>
   <si>
-    <t>ImmunizationRecommendation.recommendation.vaccineCode.extension:translation.value[x]:valueCodeableConcept.text</t>
+    <t>ImmunizationRecommendation.recommendation.vaccineCode.extension:translation.value[x].text</t>
   </si>
   <si>
     <t>ImmunizationRecommendation.recommendation.vaccineCode.extension.value[x].text</t>
@@ -1310,6 +1297,10 @@
   </si>
   <si>
     <t>The recommended number of doses to achieve immunity.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">type:$this}
+</t>
   </si>
   <si>
     <t>OBX-5 : OBX-3 = 59782-3</t>
@@ -1683,12 +1674,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN74"/>
+  <dimension ref="A1:AN73"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="109.3359375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="90.625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="81.64453125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.078125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="18.51953125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
@@ -6566,14 +6557,16 @@
         <v>77</v>
       </c>
       <c r="AB43" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AC43" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC43" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>323</v>
+        <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
         <v>171</v>
@@ -6605,20 +6598,18 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>321</v>
-      </c>
-      <c r="C44" t="s" s="2">
-        <v>325</v>
-      </c>
+        <v>323</v>
+      </c>
+      <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G44" t="s" s="2">
         <v>88</v>
@@ -6633,13 +6624,13 @@
         <v>77</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>166</v>
+        <v>148</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>167</v>
+        <v>149</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>168</v>
+        <v>150</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" s="2"/>
@@ -6690,7 +6681,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>171</v>
+        <v>151</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6702,7 +6693,7 @@
         <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>77</v>
@@ -6711,7 +6702,7 @@
         <v>77</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>77</v>
@@ -6719,21 +6710,21 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="E45" s="2"/>
       <c r="F45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G45" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H45" t="s" s="2">
         <v>77</v>
@@ -6745,15 +6736,17 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N45" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="N45" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
         <v>77</v>
@@ -6790,31 +6783,31 @@
         <v>77</v>
       </c>
       <c r="AB45" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AC45" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AD45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE45" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH45" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>77</v>
@@ -6831,14 +6824,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -6854,21 +6847,23 @@
         <v>77</v>
       </c>
       <c r="J46" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>133</v>
+        <v>182</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O46" s="2"/>
+        <v>185</v>
+      </c>
+      <c r="O46" t="s" s="2">
+        <v>186</v>
+      </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
       </c>
@@ -6904,19 +6899,19 @@
         <v>77</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AC46" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AD46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE46" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>156</v>
+        <v>187</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6928,16 +6923,16 @@
         <v>77</v>
       </c>
       <c r="AJ46" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>77</v>
+        <v>188</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>77</v>
@@ -6945,10 +6940,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -6959,7 +6954,7 @@
         <v>78</v>
       </c>
       <c r="G47" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H47" t="s" s="2">
         <v>77</v>
@@ -6968,23 +6963,19 @@
         <v>77</v>
       </c>
       <c r="J47" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>182</v>
+        <v>148</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>183</v>
+        <v>149</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="N47" t="s" s="2">
-        <v>185</v>
-      </c>
-      <c r="O47" t="s" s="2">
-        <v>186</v>
-      </c>
+        <v>150</v>
+      </c>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
         <v>77</v>
       </c>
@@ -7032,28 +7023,28 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>187</v>
+        <v>151</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH47" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>188</v>
+        <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>189</v>
+        <v>152</v>
       </c>
       <c r="AN47" t="s" s="2">
         <v>77</v>
@@ -7061,21 +7052,21 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G48" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H48" t="s" s="2">
         <v>77</v>
@@ -7087,15 +7078,17 @@
         <v>77</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N48" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="N48" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O48" s="2"/>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7132,31 +7125,31 @@
         <v>77</v>
       </c>
       <c r="AB48" t="s" s="2">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="AC48" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AD48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE48" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH48" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ48" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AK48" t="s" s="2">
         <v>77</v>
@@ -7173,21 +7166,21 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="E49" s="2"/>
       <c r="F49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G49" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H49" t="s" s="2">
         <v>77</v>
@@ -7196,21 +7189,23 @@
         <v>77</v>
       </c>
       <c r="J49" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>177</v>
+        <v>196</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O49" s="2"/>
+        <v>198</v>
+      </c>
+      <c r="O49" t="s" s="2">
+        <v>199</v>
+      </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
       </c>
@@ -7234,52 +7229,50 @@
         <v>77</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y49" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>169</v>
+      </c>
+      <c r="Y49" s="2"/>
       <c r="Z49" t="s" s="2">
-        <v>77</v>
+        <v>334</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AB49" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>155</v>
+        <v>77</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>156</v>
+        <v>201</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH49" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>77</v>
+        <v>202</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>152</v>
+        <v>203</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>77</v>
@@ -7287,10 +7280,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
+        <v>335</v>
+      </c>
+      <c r="B50" t="s" s="2">
         <v>336</v>
-      </c>
-      <c r="B50" t="s" s="2">
-        <v>337</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7313,20 +7306,18 @@
         <v>89</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="O50" t="s" s="2">
-        <v>199</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
       </c>
@@ -7350,11 +7341,13 @@
         <v>77</v>
       </c>
       <c r="X50" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="Y50" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="Y50" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="Z50" t="s" s="2">
-        <v>338</v>
+        <v>77</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>77</v>
@@ -7372,7 +7365,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7390,10 +7383,10 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>77</v>
@@ -7401,10 +7394,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7427,18 +7420,18 @@
         <v>89</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="N51" t="s" s="2">
-        <v>208</v>
-      </c>
-      <c r="O51" s="2"/>
+        <v>215</v>
+      </c>
+      <c r="N51" s="2"/>
+      <c r="O51" t="s" s="2">
+        <v>216</v>
+      </c>
       <c r="P51" t="s" s="2">
         <v>77</v>
       </c>
@@ -7486,7 +7479,7 @@
         <v>77</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7504,10 +7497,10 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>77</v>
@@ -7515,10 +7508,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7541,17 +7534,17 @@
         <v>89</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" t="s" s="2">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7600,7 +7593,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7618,10 +7611,10 @@
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>77</v>
@@ -7629,10 +7622,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7655,17 +7648,19 @@
         <v>89</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>148</v>
+        <v>230</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>223</v>
-      </c>
-      <c r="N53" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="N53" t="s" s="2">
+        <v>233</v>
+      </c>
       <c r="O53" t="s" s="2">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>77</v>
@@ -7714,7 +7709,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7732,10 +7727,10 @@
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>77</v>
@@ -7743,10 +7738,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7769,19 +7764,19 @@
         <v>89</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>230</v>
+        <v>148</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7830,7 +7825,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7848,10 +7843,10 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="AN54" t="s" s="2">
         <v>77</v>
@@ -7859,10 +7854,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -7873,7 +7868,7 @@
         <v>78</v>
       </c>
       <c r="G55" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H55" t="s" s="2">
         <v>77</v>
@@ -7885,19 +7880,19 @@
         <v>89</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>148</v>
+        <v>182</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>240</v>
+        <v>183</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>241</v>
+        <v>184</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>242</v>
+        <v>185</v>
       </c>
       <c r="O55" t="s" s="2">
-        <v>243</v>
+        <v>186</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -7946,13 +7941,13 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>244</v>
+        <v>187</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH55" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI55" t="s" s="2">
         <v>77</v>
@@ -7964,10 +7959,10 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>245</v>
+        <v>188</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>246</v>
+        <v>189</v>
       </c>
       <c r="AN55" t="s" s="2">
         <v>77</v>
@@ -7975,10 +7970,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -7989,7 +7984,7 @@
         <v>78</v>
       </c>
       <c r="G56" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H56" t="s" s="2">
         <v>77</v>
@@ -8001,19 +7996,19 @@
         <v>89</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>182</v>
+        <v>148</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>183</v>
+        <v>240</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>184</v>
+        <v>241</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>185</v>
+        <v>242</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>186</v>
+        <v>243</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8062,13 +8057,13 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>187</v>
+        <v>244</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH56" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI56" t="s" s="2">
         <v>77</v>
@@ -8080,10 +8075,10 @@
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>188</v>
+        <v>245</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>189</v>
+        <v>246</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>77</v>
@@ -8091,10 +8086,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8117,20 +8112,16 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>240</v>
+        <v>348</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>241</v>
-      </c>
-      <c r="N57" t="s" s="2">
-        <v>242</v>
-      </c>
-      <c r="O57" t="s" s="2">
-        <v>243</v>
-      </c>
+        <v>349</v>
+      </c>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
         <v>77</v>
       </c>
@@ -8154,13 +8145,13 @@
         <v>77</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>77</v>
+        <v>350</v>
       </c>
       <c r="Y57" t="s" s="2">
-        <v>77</v>
+        <v>351</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>77</v>
+        <v>352</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>77</v>
@@ -8178,7 +8169,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>244</v>
+        <v>347</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8196,10 +8187,10 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>245</v>
+        <v>304</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>246</v>
+        <v>305</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>77</v>
@@ -8207,10 +8198,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8221,7 +8212,7 @@
         <v>78</v>
       </c>
       <c r="G58" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H58" t="s" s="2">
         <v>77</v>
@@ -8236,10 +8227,10 @@
         <v>166</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8266,13 +8257,13 @@
         <v>77</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>77</v>
@@ -8290,13 +8281,13 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH58" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI58" t="s" s="2">
         <v>77</v>
@@ -8308,10 +8299,10 @@
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>304</v>
+        <v>77</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>305</v>
+        <v>77</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>77</v>
@@ -8319,10 +8310,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8330,16 +8321,16 @@
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G59" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I59" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J59" t="s" s="2">
         <v>89</v>
@@ -8348,10 +8339,10 @@
         <v>166</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8363,7 +8354,7 @@
         <v>77</v>
       </c>
       <c r="S59" t="s" s="2">
-        <v>77</v>
+        <v>361</v>
       </c>
       <c r="T59" t="s" s="2">
         <v>77</v>
@@ -8378,13 +8369,13 @@
         <v>77</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>77</v>
@@ -8402,13 +8393,13 @@
         <v>77</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG59" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH59" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI59" t="s" s="2">
         <v>77</v>
@@ -8420,10 +8411,10 @@
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>77</v>
+        <v>364</v>
       </c>
       <c r="AM59" t="s" s="2">
-        <v>77</v>
+        <v>365</v>
       </c>
       <c r="AN59" t="s" s="2">
         <v>77</v>
@@ -8431,10 +8422,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8442,16 +8433,16 @@
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G60" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I60" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J60" t="s" s="2">
         <v>89</v>
@@ -8460,10 +8451,10 @@
         <v>166</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8475,7 +8466,7 @@
         <v>77</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>365</v>
+        <v>77</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>77</v>
@@ -8490,37 +8481,37 @@
         <v>77</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="Y60" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="Z60" t="s" s="2">
+        <v>370</v>
+      </c>
+      <c r="AA60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE60" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF60" t="s" s="2">
         <v>366</v>
       </c>
-      <c r="Z60" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="AA60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE60" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF60" t="s" s="2">
-        <v>362</v>
-      </c>
       <c r="AG60" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH60" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI60" t="s" s="2">
         <v>77</v>
@@ -8532,10 +8523,10 @@
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>369</v>
+        <v>131</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>77</v>
@@ -8543,10 +8534,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8554,10 +8545,10 @@
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G61" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H61" t="s" s="2">
         <v>77</v>
@@ -8566,16 +8557,16 @@
         <v>77</v>
       </c>
       <c r="J61" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>166</v>
+        <v>286</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" s="2"/>
@@ -8602,13 +8593,13 @@
         <v>77</v>
       </c>
       <c r="X61" t="s" s="2">
-        <v>354</v>
+        <v>77</v>
       </c>
       <c r="Y61" t="s" s="2">
-        <v>373</v>
+        <v>77</v>
       </c>
       <c r="Z61" t="s" s="2">
-        <v>374</v>
+        <v>77</v>
       </c>
       <c r="AA61" t="s" s="2">
         <v>77</v>
@@ -8626,7 +8617,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8641,13 +8632,13 @@
         <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>77</v>
+        <v>375</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>131</v>
+        <v>377</v>
       </c>
       <c r="AN61" t="s" s="2">
         <v>77</v>
@@ -8655,10 +8646,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8666,7 +8657,7 @@
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G62" t="s" s="2">
         <v>88</v>
@@ -8681,13 +8672,13 @@
         <v>77</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>286</v>
+        <v>148</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>377</v>
+        <v>149</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>378</v>
+        <v>150</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8738,28 +8729,28 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>376</v>
+        <v>151</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH62" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>100</v>
+        <v>77</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>379</v>
+        <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>380</v>
+        <v>77</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>381</v>
+        <v>152</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>77</v>
@@ -8767,21 +8758,21 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>77</v>
+        <v>176</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G63" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H63" t="s" s="2">
         <v>77</v>
@@ -8793,15 +8784,17 @@
         <v>77</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>149</v>
+        <v>177</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="N63" s="2"/>
+        <v>178</v>
+      </c>
+      <c r="N63" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -8850,19 +8843,19 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH63" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>77</v>
@@ -8879,14 +8872,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>176</v>
+        <v>294</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -8899,24 +8892,26 @@
         <v>77</v>
       </c>
       <c r="I64" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="J64" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K64" t="s" s="2">
         <v>133</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>177</v>
+        <v>295</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>178</v>
+        <v>296</v>
       </c>
       <c r="N64" t="s" s="2">
         <v>179</v>
       </c>
-      <c r="O64" s="2"/>
+      <c r="O64" t="s" s="2">
+        <v>255</v>
+      </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
       </c>
@@ -8964,7 +8959,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>156</v>
+        <v>297</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -8985,7 +8980,7 @@
         <v>77</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>77</v>
@@ -8993,46 +8988,42 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
-        <v>294</v>
+        <v>77</v>
       </c>
       <c r="E65" s="2"/>
       <c r="F65" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G65" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="H65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I65" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="J65" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>133</v>
+        <v>166</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>295</v>
+        <v>382</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>296</v>
-      </c>
-      <c r="N65" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="O65" t="s" s="2">
-        <v>255</v>
-      </c>
+        <v>383</v>
+      </c>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
         <v>77</v>
       </c>
@@ -9056,13 +9047,13 @@
         <v>77</v>
       </c>
       <c r="X65" t="s" s="2">
-        <v>77</v>
+        <v>350</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>77</v>
+        <v>384</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>77</v>
+        <v>385</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>77</v>
@@ -9080,28 +9071,28 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>297</v>
+        <v>381</v>
       </c>
       <c r="AG65" t="s" s="2">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="AH65" t="s" s="2">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="AI65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>139</v>
+        <v>100</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>77</v>
+        <v>386</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>131</v>
+        <v>387</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>77</v>
@@ -9109,10 +9100,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9135,13 +9126,13 @@
         <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>166</v>
+        <v>273</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9168,31 +9159,31 @@
         <v>77</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>354</v>
+        <v>77</v>
       </c>
       <c r="Y66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE66" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF66" t="s" s="2">
         <v>388</v>
-      </c>
-      <c r="Z66" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="AA66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE66" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF66" t="s" s="2">
-        <v>385</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>88</v>
@@ -9210,10 +9201,10 @@
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>77</v>
@@ -9221,10 +9212,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9232,13 +9223,13 @@
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="G67" t="s" s="2">
         <v>88</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>77</v>
@@ -9247,13 +9238,13 @@
         <v>77</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>273</v>
+        <v>148</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9304,10 +9295,10 @@
         <v>77</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG67" t="s" s="2">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="AH67" t="s" s="2">
         <v>88</v>
@@ -9322,10 +9313,10 @@
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>77</v>
@@ -9333,10 +9324,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9350,7 +9341,7 @@
         <v>88</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>77</v>
@@ -9362,10 +9353,10 @@
         <v>148</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9416,7 +9407,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9434,10 +9425,10 @@
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>77</v>
@@ -9445,10 +9436,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9468,18 +9459,20 @@
         <v>77</v>
       </c>
       <c r="J69" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>148</v>
+        <v>404</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="N69" s="2"/>
+        <v>406</v>
+      </c>
+      <c r="N69" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
         <v>77</v>
@@ -9528,7 +9521,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9546,10 +9539,10 @@
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>77</v>
@@ -9557,10 +9550,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9580,19 +9573,19 @@
         <v>77</v>
       </c>
       <c r="J70" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -9630,19 +9623,17 @@
         <v>77</v>
       </c>
       <c r="AB70" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>77</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="AC70" s="2"/>
       <c r="AD70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE70" t="s" s="2">
-        <v>77</v>
+        <v>137</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9660,10 +9651,10 @@
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>77</v>
@@ -9671,12 +9662,14 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="C71" s="2"/>
+        <v>410</v>
+      </c>
+      <c r="C71" t="s" s="2">
+        <v>417</v>
+      </c>
       <c r="D71" t="s" s="2">
         <v>77</v>
       </c>
@@ -9688,7 +9681,7 @@
         <v>88</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>77</v>
@@ -9697,16 +9690,16 @@
         <v>77</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -9744,17 +9737,19 @@
         <v>77</v>
       </c>
       <c r="AB71" t="s" s="2">
-        <v>322</v>
-      </c>
-      <c r="AC71" s="2"/>
+        <v>77</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>77</v>
+      </c>
       <c r="AD71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE71" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9772,10 +9767,10 @@
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>77</v>
@@ -9786,11 +9781,9 @@
         <v>419</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="C72" t="s" s="2">
-        <v>420</v>
-      </c>
+        <v>419</v>
+      </c>
+      <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
         <v>77</v>
       </c>
@@ -9799,10 +9792,10 @@
         <v>78</v>
       </c>
       <c r="G72" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>77</v>
@@ -9811,17 +9804,15 @@
         <v>77</v>
       </c>
       <c r="K72" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="L72" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="L72" t="s" s="2">
-        <v>415</v>
-      </c>
       <c r="M72" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="N72" t="s" s="2">
-        <v>411</v>
-      </c>
+        <v>422</v>
+      </c>
+      <c r="N72" s="2"/>
       <c r="O72" s="2"/>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -9870,13 +9861,13 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH72" t="s" s="2">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="AI72" t="s" s="2">
         <v>77</v>
@@ -9888,10 +9879,10 @@
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>77</v>
@@ -9899,10 +9890,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -9925,13 +9916,13 @@
         <v>77</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -9982,7 +9973,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -9997,132 +9988,20 @@
         <v>100</v>
       </c>
       <c r="AK73" t="s" s="2">
-        <v>77</v>
+        <v>429</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="AM73" t="s" s="2">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="74" hidden="true">
-      <c r="A74" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="B74" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="C74" s="2"/>
-      <c r="D74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E74" s="2"/>
-      <c r="F74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K74" t="s" s="2">
-        <v>429</v>
-      </c>
-      <c r="L74" t="s" s="2">
-        <v>430</v>
-      </c>
-      <c r="M74" t="s" s="2">
-        <v>431</v>
-      </c>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
-      <c r="P74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q74" s="2"/>
-      <c r="R74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>428</v>
-      </c>
-      <c r="AG74" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH74" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI74" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ74" t="s" s="2">
-        <v>100</v>
-      </c>
-      <c r="AK74" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="AL74" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="AM74" t="s" s="2">
-        <v>434</v>
-      </c>
-      <c r="AN74" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN74">
+  <autoFilter ref="A1:AN73">
     <filterColumn colId="6">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -10132,7 +10011,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI73">
+  <conditionalFormatting sqref="A2:AI72">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>
